--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N82_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.51507186863454</v>
+        <v>7.558699178653113</v>
       </c>
       <c r="D2" t="n">
-        <v>47.19131358953247</v>
+        <v>7.668588458299027</v>
       </c>
       <c r="E2" t="n">
-        <v>3.643200437146902</v>
+        <v>0.5920200710363717</v>
       </c>
       <c r="F2" t="n">
-        <v>3.830352638496581</v>
+        <v>0.6224323037556945</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.96498474875234</v>
+        <v>6.819310021672255</v>
       </c>
       <c r="D3" t="n">
-        <v>42.27562766665156</v>
+        <v>6.869789495830879</v>
       </c>
       <c r="E3" t="n">
-        <v>3.643200437146902</v>
+        <v>0.5920200710363717</v>
       </c>
       <c r="F3" t="n">
-        <v>3.830352638496581</v>
+        <v>0.6224323037556945</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.62258445507922</v>
+        <v>7.251169973950374</v>
       </c>
       <c r="D4" t="n">
-        <v>44.38616869894833</v>
+        <v>7.212752413579104</v>
       </c>
       <c r="E4" t="n">
-        <v>3.643200437146902</v>
+        <v>0.5920200710363717</v>
       </c>
       <c r="F4" t="n">
-        <v>3.830352638496581</v>
+        <v>0.6224323037556945</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.82721766221613</v>
+        <v>5.984422870110121</v>
       </c>
       <c r="D5" t="n">
-        <v>36.74166295325702</v>
+        <v>5.970520229904266</v>
       </c>
       <c r="E5" t="n">
-        <v>3.643200437146902</v>
+        <v>0.5920200710363717</v>
       </c>
       <c r="F5" t="n">
-        <v>3.830352638496581</v>
+        <v>0.6224323037556945</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
